--- a/artfynd/A 12419-2021 artfynd.xlsx
+++ b/artfynd/A 12419-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12419-2021 artfynd.xlsx
+++ b/artfynd/A 12419-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1037,6 +1037,445 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122747428</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stenås N, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>562236</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6506839</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Relativt färska spår i två klena torrträd av tall. I sparad hänsyn.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122747427</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5023</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101608</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Asppraktbagge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecilonota variolosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Paykull, 1799)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stenås N, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>562275</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6506875</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spår i basen på gammal asp.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122747426</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stormoliden S, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>562332</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6506959</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spår i tallåga som ligger i hänsyn.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122747429</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79278</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stenås NV, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>562218</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6506726</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12419-2021 artfynd.xlsx
+++ b/artfynd/A 12419-2021 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747428</v>
+        <v>122747429</v>
       </c>
       <c r="B5" t="n">
-        <v>8441</v>
+        <v>79380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,38 +1051,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenås N, Ög</t>
+          <t>Stenås NV, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562236</v>
+        <v>562218</v>
       </c>
       <c r="R5" t="n">
-        <v>6506839</v>
+        <v>6506726</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,11 +1115,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Relativt färska spår i två klena torrträd av tall. I sparad hänsyn.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747427</v>
+        <v>122747428</v>
       </c>
       <c r="B6" t="n">
-        <v>5023</v>
+        <v>8441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,25 +1157,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101608</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562275</v>
+        <v>562236</v>
       </c>
       <c r="R6" t="n">
-        <v>6506875</v>
+        <v>6506839</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1225,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spår i basen på gammal asp.</t>
+          <t>Relativt färska spår i två klena torrträd av tall. I sparad hänsyn.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1372,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747429</v>
+        <v>122747427</v>
       </c>
       <c r="B8" t="n">
-        <v>79278</v>
+        <v>5023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,34 +1383,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>101608</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stenås NV, Ög</t>
+          <t>Stenås N, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562218</v>
+        <v>562275</v>
       </c>
       <c r="R8" t="n">
-        <v>6506726</v>
+        <v>6506875</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,6 +1443,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår i basen på gammal asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12419-2021 artfynd.xlsx
+++ b/artfynd/A 12419-2021 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747429</v>
+        <v>122747428</v>
       </c>
       <c r="B5" t="n">
-        <v>79380</v>
+        <v>8441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,38 +1051,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenås NV, Ög</t>
+          <t>Stenås N, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562218</v>
+        <v>562236</v>
       </c>
       <c r="R5" t="n">
-        <v>6506726</v>
+        <v>6506839</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,6 +1115,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Relativt färska spår i två klena torrträd av tall. I sparad hänsyn.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1150,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747428</v>
+        <v>122747426</v>
       </c>
       <c r="B6" t="n">
         <v>8441</v>
@@ -1181,14 +1186,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stenås N, Ög</t>
+          <t>Stormoliden S, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562236</v>
+        <v>562332</v>
       </c>
       <c r="R6" t="n">
-        <v>6506839</v>
+        <v>6506959</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1230,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Relativt färska spår i två klena torrträd av tall. I sparad hänsyn.</t>
+          <t>Spår i tallåga som ligger i hänsyn.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747426</v>
+        <v>122747429</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,38 +1273,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stormoliden S, Ög</t>
+          <t>Stenås NV, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562332</v>
+        <v>562218</v>
       </c>
       <c r="R7" t="n">
-        <v>6506959</v>
+        <v>6506726</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,11 +1337,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spår i tallåga som ligger i hänsyn.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 12419-2021 artfynd.xlsx
+++ b/artfynd/A 12419-2021 artfynd.xlsx
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747426</v>
+        <v>122747429</v>
       </c>
       <c r="B6" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,38 +1162,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stormoliden S, Ög</t>
+          <t>Stenås NV, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562332</v>
+        <v>562218</v>
       </c>
       <c r="R6" t="n">
-        <v>6506959</v>
+        <v>6506726</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,11 +1226,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spår i tallåga som ligger i hänsyn.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747429</v>
+        <v>122747426</v>
       </c>
       <c r="B7" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,38 +1268,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenås NV, Ög</t>
+          <t>Stormoliden S, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562218</v>
+        <v>562332</v>
       </c>
       <c r="R7" t="n">
-        <v>6506726</v>
+        <v>6506959</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,6 +1332,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spår i tallåga som ligger i hänsyn.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 12419-2021 artfynd.xlsx
+++ b/artfynd/A 12419-2021 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747428</v>
+        <v>122747429</v>
       </c>
       <c r="B5" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,38 +1051,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenås N, Ög</t>
+          <t>Stenås NV, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562236</v>
+        <v>562218</v>
       </c>
       <c r="R5" t="n">
-        <v>6506839</v>
+        <v>6506726</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,11 +1115,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Relativt färska spår i två klena torrträd av tall. I sparad hänsyn.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747429</v>
+        <v>122747428</v>
       </c>
       <c r="B6" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,38 +1157,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stenås NV, Ög</t>
+          <t>Stenås N, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562218</v>
+        <v>562236</v>
       </c>
       <c r="R6" t="n">
-        <v>6506726</v>
+        <v>6506839</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,6 +1221,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Relativt färska spår i två klena torrträd av tall. I sparad hänsyn.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747426</v>
+        <v>122747427</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>5023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,38 +1268,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>101608</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stormoliden S, Ög</t>
+          <t>Stenås N, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562332</v>
+        <v>562275</v>
       </c>
       <c r="R7" t="n">
-        <v>6506959</v>
+        <v>6506875</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spår i tallåga som ligger i hänsyn.</t>
+          <t>Spår i basen på gammal asp.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747427</v>
+        <v>122747426</v>
       </c>
       <c r="B8" t="n">
-        <v>5023</v>
+        <v>8441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,38 +1379,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101608</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stenås N, Ög</t>
+          <t>Stormoliden S, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562275</v>
+        <v>562332</v>
       </c>
       <c r="R8" t="n">
-        <v>6506875</v>
+        <v>6506959</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spår i basen på gammal asp.</t>
+          <t>Spår i tallåga som ligger i hänsyn.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12419-2021 artfynd.xlsx
+++ b/artfynd/A 12419-2021 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747429</v>
+        <v>122747426</v>
       </c>
       <c r="B5" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,38 +1051,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenås NV, Ög</t>
+          <t>Stormoliden S, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562218</v>
+        <v>562332</v>
       </c>
       <c r="R5" t="n">
-        <v>6506726</v>
+        <v>6506959</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,6 +1115,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spår i tallåga som ligger i hänsyn.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1256,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747427</v>
+        <v>122747429</v>
       </c>
       <c r="B7" t="n">
-        <v>5023</v>
+        <v>79384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,34 +1277,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101608</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenås N, Ög</t>
+          <t>Stenås NV, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562275</v>
+        <v>562218</v>
       </c>
       <c r="R7" t="n">
-        <v>6506875</v>
+        <v>6506726</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,11 +1337,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spår i basen på gammal asp.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747426</v>
+        <v>122747427</v>
       </c>
       <c r="B8" t="n">
-        <v>8441</v>
+        <v>5023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,38 +1379,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>101608</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stormoliden S, Ög</t>
+          <t>Stenås N, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562332</v>
+        <v>562275</v>
       </c>
       <c r="R8" t="n">
-        <v>6506959</v>
+        <v>6506875</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spår i tallåga som ligger i hänsyn.</t>
+          <t>Spår i basen på gammal asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12419-2021 artfynd.xlsx
+++ b/artfynd/A 12419-2021 artfynd.xlsx
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747428</v>
+        <v>122747427</v>
       </c>
       <c r="B6" t="n">
-        <v>8441</v>
+        <v>5023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,25 +1162,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>101608</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562236</v>
+        <v>562275</v>
       </c>
       <c r="R6" t="n">
-        <v>6506839</v>
+        <v>6506875</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Relativt färska spår i två klena torrträd av tall. I sparad hänsyn.</t>
+          <t>Spår i basen på gammal asp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747429</v>
+        <v>122747428</v>
       </c>
       <c r="B7" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,38 +1273,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenås NV, Ög</t>
+          <t>Stenås N, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562218</v>
+        <v>562236</v>
       </c>
       <c r="R7" t="n">
-        <v>6506726</v>
+        <v>6506839</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,6 +1337,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Relativt färska spår i två klena torrträd av tall. I sparad hänsyn.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747427</v>
+        <v>122747429</v>
       </c>
       <c r="B8" t="n">
-        <v>5023</v>
+        <v>79384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1388,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101608</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stenås N, Ög</t>
+          <t>Stenås NV, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562275</v>
+        <v>562218</v>
       </c>
       <c r="R8" t="n">
-        <v>6506875</v>
+        <v>6506726</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,11 +1448,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spår i basen på gammal asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12419-2021 artfynd.xlsx
+++ b/artfynd/A 12419-2021 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747426</v>
+        <v>122747427</v>
       </c>
       <c r="B5" t="n">
-        <v>8441</v>
+        <v>5023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,38 +1051,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>101608</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stormoliden S, Ög</t>
+          <t>Stenås N, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562332</v>
+        <v>562275</v>
       </c>
       <c r="R5" t="n">
-        <v>6506959</v>
+        <v>6506875</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spår i tallåga som ligger i hänsyn.</t>
+          <t>Spår i basen på gammal asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747427</v>
+        <v>122747429</v>
       </c>
       <c r="B6" t="n">
-        <v>5023</v>
+        <v>79384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,34 +1166,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101608</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stenås N, Ög</t>
+          <t>Stenås NV, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562275</v>
+        <v>562218</v>
       </c>
       <c r="R6" t="n">
-        <v>6506875</v>
+        <v>6506726</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,11 +1226,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spår i basen på gammal asp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1372,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747429</v>
+        <v>122747426</v>
       </c>
       <c r="B8" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,38 +1379,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stenås NV, Ög</t>
+          <t>Stormoliden S, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562218</v>
+        <v>562332</v>
       </c>
       <c r="R8" t="n">
-        <v>6506726</v>
+        <v>6506959</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,6 +1443,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår i tallåga som ligger i hänsyn.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12419-2021 artfynd.xlsx
+++ b/artfynd/A 12419-2021 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747427</v>
+        <v>122747429</v>
       </c>
       <c r="B5" t="n">
-        <v>5023</v>
+        <v>79384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,34 +1055,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101608</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenås N, Ög</t>
+          <t>Stenås NV, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562275</v>
+        <v>562218</v>
       </c>
       <c r="R5" t="n">
-        <v>6506875</v>
+        <v>6506726</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,11 +1115,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spår i basen på gammal asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747429</v>
+        <v>122747426</v>
       </c>
       <c r="B6" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,38 +1157,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stenås NV, Ög</t>
+          <t>Stormoliden S, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562218</v>
+        <v>562332</v>
       </c>
       <c r="R6" t="n">
-        <v>6506726</v>
+        <v>6506959</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,6 +1221,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spår i tallåga som ligger i hänsyn.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747428</v>
+        <v>122747427</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>5023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,25 +1268,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>101608</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562236</v>
+        <v>562275</v>
       </c>
       <c r="R7" t="n">
-        <v>6506839</v>
+        <v>6506875</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Relativt färska spår i två klena torrträd av tall. I sparad hänsyn.</t>
+          <t>Spår i basen på gammal asp.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747426</v>
+        <v>122747428</v>
       </c>
       <c r="B8" t="n">
         <v>8441</v>
@@ -1403,14 +1403,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stormoliden S, Ög</t>
+          <t>Stenås N, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562332</v>
+        <v>562236</v>
       </c>
       <c r="R8" t="n">
-        <v>6506959</v>
+        <v>6506839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spår i tallåga som ligger i hänsyn.</t>
+          <t>Relativt färska spår i två klena torrträd av tall. I sparad hänsyn.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12419-2021 artfynd.xlsx
+++ b/artfynd/A 12419-2021 artfynd.xlsx
@@ -1256,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747427</v>
+        <v>122747428</v>
       </c>
       <c r="B7" t="n">
-        <v>5023</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,25 +1268,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101608</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562275</v>
+        <v>562236</v>
       </c>
       <c r="R7" t="n">
-        <v>6506875</v>
+        <v>6506839</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spår i basen på gammal asp.</t>
+          <t>Relativt färska spår i två klena torrträd av tall. I sparad hänsyn.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747428</v>
+        <v>122747427</v>
       </c>
       <c r="B8" t="n">
-        <v>8441</v>
+        <v>5023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,25 +1379,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>101608</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562236</v>
+        <v>562275</v>
       </c>
       <c r="R8" t="n">
-        <v>6506839</v>
+        <v>6506875</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Relativt färska spår i två klena torrträd av tall. I sparad hänsyn.</t>
+          <t>Spår i basen på gammal asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12419-2021 artfynd.xlsx
+++ b/artfynd/A 12419-2021 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747429</v>
+        <v>122747427</v>
       </c>
       <c r="B5" t="n">
-        <v>79384</v>
+        <v>5023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,34 +1055,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>101608</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenås NV, Ög</t>
+          <t>Stenås N, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562218</v>
+        <v>562275</v>
       </c>
       <c r="R5" t="n">
-        <v>6506726</v>
+        <v>6506875</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,6 +1115,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spår i basen på gammal asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1367,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747427</v>
+        <v>122747429</v>
       </c>
       <c r="B8" t="n">
-        <v>5023</v>
+        <v>79387</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1388,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101608</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stenås N, Ög</t>
+          <t>Stenås NV, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562275</v>
+        <v>562218</v>
       </c>
       <c r="R8" t="n">
-        <v>6506875</v>
+        <v>6506726</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,11 +1448,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spår i basen på gammal asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12419-2021 artfynd.xlsx
+++ b/artfynd/A 12419-2021 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747427</v>
+        <v>122747429</v>
       </c>
       <c r="B5" t="n">
-        <v>5023</v>
+        <v>79389</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,34 +1055,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101608</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenås N, Ög</t>
+          <t>Stenås NV, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562275</v>
+        <v>562218</v>
       </c>
       <c r="R5" t="n">
-        <v>6506875</v>
+        <v>6506726</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,11 +1115,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spår i basen på gammal asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747426</v>
+        <v>122747427</v>
       </c>
       <c r="B6" t="n">
-        <v>8441</v>
+        <v>5023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,38 +1157,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>101608</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stormoliden S, Ög</t>
+          <t>Stenås N, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562332</v>
+        <v>562275</v>
       </c>
       <c r="R6" t="n">
-        <v>6506959</v>
+        <v>6506875</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1225,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spår i tallåga som ligger i hänsyn.</t>
+          <t>Spår i basen på gammal asp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1256,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747428</v>
+        <v>122747426</v>
       </c>
       <c r="B7" t="n">
         <v>8441</v>
@@ -1297,14 +1292,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenås N, Ög</t>
+          <t>Stormoliden S, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562236</v>
+        <v>562332</v>
       </c>
       <c r="R7" t="n">
-        <v>6506839</v>
+        <v>6506959</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1336,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Relativt färska spår i två klena torrträd av tall. I sparad hänsyn.</t>
+          <t>Spår i tallåga som ligger i hänsyn.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747429</v>
+        <v>122747428</v>
       </c>
       <c r="B8" t="n">
-        <v>79387</v>
+        <v>8441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,38 +1379,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stenås NV, Ög</t>
+          <t>Stenås N, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562218</v>
+        <v>562236</v>
       </c>
       <c r="R8" t="n">
-        <v>6506726</v>
+        <v>6506839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,6 +1443,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Relativt färska spår i två klena torrträd av tall. I sparad hänsyn.</t>
         </is>
       </c>
       <c r="AD8" t="b">
